--- a/inst/extdata/2drugs_warnings.xlsx
+++ b/inst/extdata/2drugs_warnings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mathilde.robin\Documents\__Treatment resistance\Team tools\EDITH\inst\extdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{862F5532-1A72-4867-BA5C-18D2A380A78E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CF384F1-8D88-4E8D-B218-DE94247831DB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="17250" windowHeight="5775" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
